--- a/AtchisonRegime/Outputs/Brazil/df_regInflation_Brazil.xlsx
+++ b/AtchisonRegime/Outputs/Brazil/df_regInflation_Brazil.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H498"/>
+  <dimension ref="A1:H499"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13377,24 +13377,50 @@
         <v>45747</v>
       </c>
       <c r="B498" t="n">
-        <v>5.06</v>
+        <v>5.48</v>
       </c>
       <c r="C498" t="n">
-        <v>4.893333333333636</v>
+        <v>5.033333333333636</v>
       </c>
       <c r="D498" t="n">
-        <v>5.616111111111111</v>
+        <v>5.627777777777777</v>
       </c>
       <c r="E498" t="n">
-        <v>2.343134991274868</v>
+        <v>2.341331868973302</v>
       </c>
       <c r="F498" t="b">
         <v>0</v>
       </c>
       <c r="G498" t="n">
-        <v>-0.3084661278453371</v>
+        <v>-0.253891578687139</v>
       </c>
       <c r="H498" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="2" t="n">
+        <v>45777</v>
+      </c>
+      <c r="B499" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="C499" t="n">
+        <v>5.340000000000303</v>
+      </c>
+      <c r="D499" t="n">
+        <v>5.443055555555556</v>
+      </c>
+      <c r="E499" t="n">
+        <v>2.058978691974066</v>
+      </c>
+      <c r="F499" t="b">
+        <v>0</v>
+      </c>
+      <c r="G499" t="n">
+        <v>-0.05005178341911259</v>
+      </c>
+      <c r="H499" t="b">
         <v>0</v>
       </c>
     </row>
